--- a/Result/profitability/2528.xlsx
+++ b/Result/profitability/2528.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9037500000000001</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>30.2475</v>
+        <v>29.84375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.5175</v>
       </c>
       <c r="N3" t="n">
-        <v>27.15</v>
+        <v>26.08499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.435</v>
+        <v>0.3825</v>
       </c>
       <c r="N4" t="n">
-        <v>23.72</v>
+        <v>24.51375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2825</v>
+        <v>0.27375</v>
       </c>
       <c r="N5" t="n">
-        <v>21.07375</v>
+        <v>22.73249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1875</v>
+        <v>0.0725</v>
       </c>
       <c r="N6" t="n">
-        <v>21.65624999999999</v>
+        <v>23.47874999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02</v>
+        <v>0.02374999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>22.55749999999999</v>
+        <v>24.7125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0575</v>
+        <v>0.03874999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>21.63999999999999</v>
+        <v>24.75875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1522,10 +1522,10 @@
         <v>0.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03375</v>
+        <v>0.03374999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>24.98124999999999</v>
+        <v>24.98125</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1649,7 +1649,7 @@
         <v>-0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04625</v>
+        <v>0.04624999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>22.11</v>
@@ -2030,7 +2030,7 @@
         <v>-0.29</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002500000000000002</v>
+        <v>0.002499999999999995</v>
       </c>
       <c r="N13" t="n">
         <v>41.86499999999999</v>
@@ -9776,6 +9776,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1658</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E75" t="n">
+        <v>545</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>432</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>407</v>
+      </c>
+      <c r="K75" t="n">
+        <v>330</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>3.150252525252525</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.06999999999999995</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09589041095890405</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6770408163265305</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
